--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="183">
   <si>
     <t>Materia</t>
   </si>
@@ -206,24 +206,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Loyo Sanchez Raul Manuel</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Loyo Sanchez Raul Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -251,316 +251,316 @@
     <t>DECTOR</t>
   </si>
   <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SOBRINO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ALDUZIN</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>KARLOS ARATH</t>
+  </si>
+  <si>
+    <t>ANDRICK YAEL</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>BRANDON ADALID</t>
+  </si>
+  <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
     <t>GAMBOA</t>
   </si>
   <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAYTAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MARES</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>SOBRINO</t>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>TEPOLE</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ALDUZIN</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>APOLINAR</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>GROT</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>TETLACTLE</t>
   </si>
   <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>ALDO EMANUEL</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
+    <t>PULIDO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>AZURA</t>
+  </si>
+  <si>
+    <t>ANA SHECIT</t>
+  </si>
+  <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>JOSAVIA ARIDAI</t>
   </si>
   <si>
     <t>CRHIS AMINADAB</t>
   </si>
   <si>
-    <t>KARLOS ARATH</t>
-  </si>
-  <si>
-    <t>ANDRICK YAEL</t>
-  </si>
-  <si>
-    <t>JARET</t>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
   </si>
   <si>
     <t>MARIA ANGELES</t>
   </si>
   <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>BRENDA</t>
+  </si>
+  <si>
+    <t>LUISA MARIA</t>
+  </si>
+  <si>
+    <t>LILIAN</t>
+  </si>
+  <si>
+    <t>JULIO ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE ALBIN</t>
+  </si>
+  <si>
+    <t>ATZIN LUCERO</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
-    <t>JOSE ALDAIR</t>
-  </si>
-  <si>
-    <t>AILYN</t>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
+    <t>JOSE JAVIER</t>
+  </si>
+  <si>
+    <t>NOEMI DEL ROCIO</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
   </si>
   <si>
     <t>HAZEL</t>
   </si>
   <si>
-    <t>BRANDON ADALID</t>
+    <t>KAREN ARLET</t>
+  </si>
+  <si>
+    <t>KAREN</t>
   </si>
   <si>
     <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>APOLINAR</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>AZURA</t>
-  </si>
-  <si>
-    <t>ANA SHECIT</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>ARACELI</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>LILIAN</t>
-  </si>
-  <si>
-    <t>JULIO ANTONIO</t>
-  </si>
-  <si>
-    <t>JOSE ALBIN</t>
-  </si>
-  <si>
-    <t>ATZIN LUCERO</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>JOSE JAVIER</t>
-  </si>
-  <si>
-    <t>NOEMI DEL ROCIO</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
-  </si>
-  <si>
-    <t>KAREN ARLET</t>
-  </si>
-  <si>
-    <t>KAREN</t>
   </si>
   <si>
     <t>JUAN EMANUEL</t>
@@ -1058,10 +1058,10 @@
         <v>-1</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>7</v>
@@ -1076,7 +1076,7 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1112,10 +1112,10 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1150,10 +1150,10 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1186,7 +1186,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -1227,10 +1227,10 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1263,10 +1263,10 @@
         <v>6</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1307,7 +1307,7 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1384,7 +1384,7 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1420,7 +1420,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1458,10 +1458,10 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1494,10 +1494,10 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1535,10 +1535,10 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1571,10 +1571,10 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1600,7 +1600,7 @@
         <v>6</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -1615,7 +1615,7 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1654,7 +1654,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>8</v>
@@ -1689,10 +1689,10 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1766,10 +1766,10 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1805,7 +1805,7 @@
         <v>8</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1828,10 +1828,10 @@
         <v>-1</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -1846,7 +1846,7 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1882,10 +1882,10 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -1908,7 +1908,7 @@
         <v>6</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>8</v>
@@ -1920,10 +1920,10 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1962,7 +1962,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1997,10 +1997,10 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -2036,7 +2036,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2074,10 +2074,10 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2113,7 +2113,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2151,10 +2151,10 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2190,7 +2190,7 @@
         <v>7</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2213,10 +2213,10 @@
         <v>-1</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F19">
         <v>7</v>
@@ -2231,7 +2231,7 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2267,10 +2267,10 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2293,7 +2293,7 @@
         <v>7</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>7</v>
@@ -2308,7 +2308,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2344,10 +2344,10 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>7</v>
@@ -2364,7 +2364,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -2382,10 +2382,10 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2418,10 +2418,10 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2459,10 +2459,10 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2495,10 +2495,10 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2536,10 +2536,10 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2572,10 +2572,10 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2613,10 +2613,10 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2690,10 +2690,10 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2726,7 +2726,7 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2770,7 +2770,7 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2806,7 +2806,7 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2844,10 +2844,10 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2921,10 +2921,10 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -3001,7 +3001,7 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -3037,7 +3037,7 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3075,10 +3075,10 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3111,10 +3111,10 @@
         <v>7</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3152,10 +3152,10 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3188,7 +3188,7 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -3214,7 +3214,7 @@
         <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -3229,10 +3229,10 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3268,7 +3268,7 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3291,7 +3291,7 @@
         <v>-1</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E33">
         <v>5</v>
@@ -3309,7 +3309,7 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3345,7 +3345,7 @@
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W33">
         <v>5</v>
@@ -3383,10 +3383,10 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3419,7 +3419,7 @@
         <v>6</v>
       </c>
       <c r="U34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -3460,10 +3460,10 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3496,7 +3496,7 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3537,10 +3537,10 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3576,7 +3576,7 @@
         <v>6</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3599,10 +3599,10 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F37">
         <v>8</v>
@@ -3614,10 +3614,10 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3653,10 +3653,10 @@
         <v>6</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X37">
         <v>8</v>
@@ -3676,7 +3676,7 @@
         <v>8</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E38">
         <v>7</v>
@@ -3691,10 +3691,10 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -3727,10 +3727,10 @@
         <v>5</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>7</v>
@@ -3768,10 +3768,10 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -3804,10 +3804,10 @@
         <v>7</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>9</v>
@@ -3830,7 +3830,7 @@
         <v>-1</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E40">
         <v>5</v>
@@ -3848,7 +3848,7 @@
         <v>-1</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K40">
         <v>-1</v>
@@ -3884,7 +3884,7 @@
         <v>-1</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W40">
         <v>5</v>
@@ -3907,10 +3907,10 @@
         <v>6</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F41">
         <v>8</v>
@@ -3922,10 +3922,10 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K41">
         <v>-1</v>
@@ -3961,10 +3961,10 @@
         <v>6</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X41">
         <v>8</v>
@@ -3999,10 +3999,10 @@
         <v>-1</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K42">
         <v>-1</v>
@@ -4035,10 +4035,10 @@
         <v>7</v>
       </c>
       <c r="U42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W42">
         <v>7</v>
@@ -4076,10 +4076,10 @@
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K43">
         <v>-1</v>
@@ -4115,7 +4115,7 @@
         <v>9</v>
       </c>
       <c r="V43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W43">
         <v>9</v>
@@ -4153,10 +4153,10 @@
         <v>-1</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K44">
         <v>-1</v>
@@ -4189,7 +4189,7 @@
         <v>7</v>
       </c>
       <c r="U44">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V44">
         <v>9</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -4269,27 +4269,27 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>75.61</v>
       </c>
       <c r="G2">
+        <v>19.51</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
         <v>4.88</v>
-      </c>
-      <c r="H2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>19.51</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -4298,30 +4298,30 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>75.61</v>
+        <v>78.05</v>
       </c>
       <c r="G3">
+        <v>2.44</v>
+      </c>
+      <c r="H3">
+        <v>7.3</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
+      </c>
+      <c r="J3">
         <v>19.51</v>
-      </c>
-      <c r="H3">
-        <v>6.4</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>4.88</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -4330,30 +4330,30 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>78.05</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J4">
-        <v>21.95</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -4362,30 +4362,30 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>78.05</v>
+        <v>87.8</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="H5">
         <v>7.2</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>21.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -4394,30 +4394,30 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>80.48999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
         <v>12.2</v>
-      </c>
-      <c r="H6">
-        <v>6.6</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>7.32</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -4426,25 +4426,25 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="G7">
+        <v>9.76</v>
+      </c>
+      <c r="H7">
+        <v>7.8</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>87.8</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>12.2</v>
       </c>
     </row>
   </sheetData>
@@ -4454,7 +4454,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4489,716 +4489,356 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920396</v>
+        <v>22330051920231</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920396</v>
+        <v>22330051920232</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920231</v>
+        <v>22330051920233</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920232</v>
+        <v>22330051920236</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920233</v>
+        <v>22330051920422</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920236</v>
+        <v>22330051920422</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920236</v>
+        <v>22330051920422</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920239</v>
+        <v>22330051920398</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920422</v>
+        <v>22330051920398</v>
       </c>
       <c r="B11" t="s">
         <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920422</v>
+        <v>22330051920357</v>
       </c>
       <c r="B12" t="s">
         <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920422</v>
+        <v>22330051920357</v>
       </c>
       <c r="B13" t="s">
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920422</v>
+        <v>22330051920376</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920422</v>
+        <v>22330051920376</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920398</v>
+        <v>22330051920366</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920398</v>
+        <v>22330051920255</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920398</v>
+        <v>22330051920255</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
         <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920398</v>
+        <v>22330051920255</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920357</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920357</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920357</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920243</v>
-      </c>
-      <c r="B23" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" t="s">
-        <v>110</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920399</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920376</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" t="s">
-        <v>112</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920376</v>
-      </c>
-      <c r="B26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920376</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920366</v>
-      </c>
-      <c r="B28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920366</v>
-      </c>
-      <c r="B29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" t="s">
-        <v>113</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920366</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>113</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920368</v>
-      </c>
-      <c r="B31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" t="s">
-        <v>114</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920255</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>99</v>
-      </c>
-      <c r="D32" t="s">
-        <v>115</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920255</v>
-      </c>
-      <c r="B33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920255</v>
-      </c>
-      <c r="B34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" t="s">
-        <v>115</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920255</v>
-      </c>
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" t="s">
-        <v>115</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920256</v>
-      </c>
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" t="s">
-        <v>100</v>
-      </c>
-      <c r="D36" t="s">
-        <v>116</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920256</v>
-      </c>
-      <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" t="s">
-        <v>100</v>
-      </c>
-      <c r="D37" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5237,166 +4877,166 @@
         <v>22330051920422</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920398</v>
+        <v>22330051920255</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920255</v>
+        <v>22330051920398</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
         <v>99</v>
       </c>
-      <c r="D4" t="s">
-        <v>115</v>
-      </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920396</v>
+        <v>22330051920357</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920357</v>
+        <v>22330051920376</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920376</v>
+        <v>22330051920396</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920366</v>
+        <v>22330051920231</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920236</v>
+        <v>22330051920232</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920256</v>
+        <v>22330051920233</v>
       </c>
       <c r="B10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" t="s">
         <v>85</v>
       </c>
-      <c r="C10" t="s">
-        <v>100</v>
-      </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920231</v>
+        <v>22330051920236</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5404,16 +5044,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920232</v>
+        <v>22330051920366</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5421,98 +5061,98 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920233</v>
+        <v>22330051920230</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920239</v>
+        <v>22330051920234</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920243</v>
+        <v>22330051920237</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920399</v>
+        <v>22330051920238</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920368</v>
+        <v>22330051920239</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920230</v>
+        <v>22330051920240</v>
       </c>
       <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" t="s">
         <v>117</v>
-      </c>
-      <c r="C18" t="s">
-        <v>141</v>
       </c>
       <c r="D18" t="s">
         <v>158</v>
@@ -5523,13 +5163,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920234</v>
+        <v>22330051920241</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="D19" t="s">
         <v>159</v>
@@ -5540,13 +5180,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920237</v>
+        <v>22330051920242</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="D20" t="s">
         <v>160</v>
@@ -5557,13 +5197,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920238</v>
+        <v>22330051920243</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="D21" t="s">
         <v>161</v>
@@ -5574,13 +5214,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920240</v>
+        <v>22330051920245</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="D22" t="s">
         <v>162</v>
@@ -5591,13 +5231,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920241</v>
+        <v>22330051920369</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D23" t="s">
         <v>163</v>
@@ -5608,13 +5248,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920242</v>
+        <v>22330051920318</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
         <v>164</v>
@@ -5625,13 +5265,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920245</v>
+        <v>22330051920319</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C25" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
         <v>165</v>
@@ -5642,13 +5282,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920369</v>
+        <v>22330051920246</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D26" t="s">
         <v>166</v>
@@ -5659,13 +5299,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920318</v>
+        <v>22330051920249</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D27" t="s">
         <v>167</v>
@@ -5676,13 +5316,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920319</v>
+        <v>22330051920414</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
         <v>168</v>
@@ -5693,13 +5333,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920246</v>
+        <v>22330051920248</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D29" t="s">
         <v>169</v>
@@ -5710,13 +5350,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920249</v>
+        <v>22330051920250</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
         <v>170</v>
@@ -5727,13 +5367,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920414</v>
+        <v>22330051920251</v>
       </c>
       <c r="B31" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="D31" t="s">
         <v>171</v>
@@ -5744,13 +5384,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920248</v>
+        <v>22330051920399</v>
       </c>
       <c r="B32" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D32" t="s">
         <v>172</v>
@@ -5761,13 +5401,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920250</v>
+        <v>22330051920400</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="D33" t="s">
         <v>173</v>
@@ -5778,13 +5418,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920251</v>
+        <v>22330051920252</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D34" t="s">
         <v>174</v>
@@ -5795,13 +5435,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920400</v>
+        <v>22330051920253</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s">
         <v>175</v>
@@ -5812,13 +5452,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920252</v>
+        <v>22330051920235</v>
       </c>
       <c r="B36" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C36" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D36" t="s">
         <v>176</v>
@@ -5829,13 +5469,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920253</v>
+        <v>22330051920368</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="D37" t="s">
         <v>177</v>
@@ -5846,13 +5486,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920235</v>
+        <v>22330051920254</v>
       </c>
       <c r="B38" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C38" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="D38" t="s">
         <v>178</v>
@@ -5863,13 +5503,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>22330051920254</v>
+        <v>22330051920257</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s">
         <v>179</v>
@@ -5880,13 +5520,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>22330051920257</v>
+        <v>22330051920256</v>
       </c>
       <c r="B40" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C40" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D40" t="s">
         <v>180</v>
@@ -5900,10 +5540,10 @@
         <v>22330051920401</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D41" t="s">
         <v>181</v>
@@ -5917,10 +5557,10 @@
         <v>22330051920259</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C42" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D42" t="s">
         <v>182</v>
@@ -5936,7 +5576,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5968,91 +5608,91 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920368</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>63</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920368</v>
+        <v>22330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>64</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920231</v>
+        <v>22330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
         <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920232</v>
+        <v>22330051920366</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6060,22 +5700,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920233</v>
+        <v>22330051920231</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -6083,22 +5723,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920243</v>
+        <v>22330051920232</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
         <v>95</v>
       </c>
-      <c r="D7" t="s">
-        <v>110</v>
-      </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6106,25 +5746,94 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920399</v>
+        <v>22330051920233</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
         <v>96</v>
       </c>
-      <c r="D8" t="s">
-        <v>111</v>
-      </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920243</v>
+      </c>
+      <c r="B9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920368</v>
+      </c>
+      <c r="B10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920256</v>
+      </c>
+      <c r="B11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -1082,7 +1082,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1118,7 +1118,7 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -1159,7 +1159,7 @@
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1195,7 +1195,7 @@
         <v>9</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1313,7 +1313,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1349,7 +1349,7 @@
         <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1467,7 +1467,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1503,7 +1503,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1544,7 +1544,7 @@
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1580,7 +1580,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1621,7 +1621,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1657,7 +1657,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>5</v>
@@ -1698,7 +1698,7 @@
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1734,7 +1734,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1775,7 +1775,7 @@
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1811,7 +1811,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1929,7 +1929,7 @@
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1965,7 +1965,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>5</v>
@@ -2006,7 +2006,7 @@
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2042,7 +2042,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -2083,7 +2083,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2119,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2196,7 +2196,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -2237,7 +2237,7 @@
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2273,7 +2273,7 @@
         <v>6</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>-1</v>
@@ -2314,7 +2314,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2350,7 +2350,7 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>-1</v>
@@ -2391,7 +2391,7 @@
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2427,7 +2427,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2468,7 +2468,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2504,7 +2504,7 @@
         <v>8</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2545,7 +2545,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2581,7 +2581,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2622,7 +2622,7 @@
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2658,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2699,7 +2699,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2735,7 +2735,7 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
         <v>6</v>
@@ -2776,7 +2776,7 @@
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2812,7 +2812,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>6</v>
@@ -2853,7 +2853,7 @@
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2889,7 +2889,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2930,7 +2930,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2966,7 +2966,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -3007,7 +3007,7 @@
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3043,7 +3043,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -3084,7 +3084,7 @@
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3120,7 +3120,7 @@
         <v>10</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -3161,7 +3161,7 @@
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3197,7 +3197,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3238,7 +3238,7 @@
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3274,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3392,7 +3392,7 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3428,7 +3428,7 @@
         <v>10</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3469,7 +3469,7 @@
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3505,7 +3505,7 @@
         <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3546,7 +3546,7 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3582,7 +3582,7 @@
         <v>7</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3623,7 +3623,7 @@
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3659,7 +3659,7 @@
         <v>6</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>-1</v>
@@ -3700,7 +3700,7 @@
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3736,7 +3736,7 @@
         <v>7</v>
       </c>
       <c r="X38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y38">
         <v>7</v>
@@ -3777,7 +3777,7 @@
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3931,7 +3931,7 @@
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3967,7 +3967,7 @@
         <v>6</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y41">
         <v>6</v>
@@ -4008,7 +4008,7 @@
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -4044,7 +4044,7 @@
         <v>7</v>
       </c>
       <c r="X42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>6</v>
@@ -4085,7 +4085,7 @@
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4121,7 +4121,7 @@
         <v>9</v>
       </c>
       <c r="X43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y43">
         <v>6</v>
@@ -4162,7 +4162,7 @@
         <v>-1</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M44">
         <v>-1</v>
@@ -4198,7 +4198,7 @@
         <v>9</v>
       </c>
       <c r="X44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y44">
         <v>6</v>
@@ -4406,7 +4406,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
         <v>5</v>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="183">
   <si>
     <t>Materia</t>
   </si>
@@ -215,13 +215,13 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
     <t>Loyo Sanchez Raul Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>NC</t>
@@ -1079,7 +1079,7 @@
         <v>4</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -1156,7 +1156,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1192,7 +1192,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1233,7 +1233,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1269,7 +1269,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>-1</v>
@@ -1310,7 +1310,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -1387,7 +1387,7 @@
         <v>4</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1464,7 +1464,7 @@
         <v>4</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1500,7 +1500,7 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1541,7 +1541,7 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>10</v>
@@ -1577,7 +1577,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1618,7 +1618,7 @@
         <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1654,7 +1654,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1695,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -1731,7 +1731,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1772,7 +1772,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1808,7 +1808,7 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1849,7 +1849,7 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1926,7 +1926,7 @@
         <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -2003,7 +2003,7 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -2080,7 +2080,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -2116,7 +2116,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -2157,7 +2157,7 @@
         <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -2193,7 +2193,7 @@
         <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2234,7 +2234,7 @@
         <v>4</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>8</v>
@@ -2270,7 +2270,7 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2311,7 +2311,7 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>8</v>
@@ -2388,7 +2388,7 @@
         <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>10</v>
@@ -2465,7 +2465,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2501,7 +2501,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2542,7 +2542,7 @@
         <v>5</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -2578,7 +2578,7 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>9</v>
@@ -2619,7 +2619,7 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -2655,7 +2655,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2696,7 +2696,7 @@
         <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2732,7 +2732,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2773,7 +2773,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>9</v>
@@ -2850,7 +2850,7 @@
         <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -2886,7 +2886,7 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2927,7 +2927,7 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -3004,7 +3004,7 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
         <v>10</v>
@@ -3040,7 +3040,7 @@
         <v>9</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -3081,7 +3081,7 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
         <v>9</v>
@@ -3117,7 +3117,7 @@
         <v>7</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -3158,7 +3158,7 @@
         <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>10</v>
@@ -3235,7 +3235,7 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>10</v>
@@ -3271,7 +3271,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -3312,7 +3312,7 @@
         <v>4</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3389,7 +3389,7 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
         <v>10</v>
@@ -3466,7 +3466,7 @@
         <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -3543,7 +3543,7 @@
         <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>9</v>
@@ -3620,7 +3620,7 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
         <v>9</v>
@@ -3656,7 +3656,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -3697,7 +3697,7 @@
         <v>6</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>10</v>
@@ -3733,7 +3733,7 @@
         <v>6</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -3774,7 +3774,7 @@
         <v>9</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>10</v>
@@ -3810,7 +3810,7 @@
         <v>9</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>10</v>
@@ -3851,7 +3851,7 @@
         <v>4</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -3928,7 +3928,7 @@
         <v>8</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L41">
         <v>9</v>
@@ -4005,7 +4005,7 @@
         <v>8</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L42">
         <v>9</v>
@@ -4041,7 +4041,7 @@
         <v>7</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>9</v>
@@ -4082,7 +4082,7 @@
         <v>9</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L43">
         <v>9</v>
@@ -4118,7 +4118,7 @@
         <v>9</v>
       </c>
       <c r="W43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X43">
         <v>9</v>
@@ -4159,7 +4159,7 @@
         <v>8</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L44">
         <v>10</v>
@@ -4195,7 +4195,7 @@
         <v>9</v>
       </c>
       <c r="W44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>10</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -4362,19 +4362,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>87.8</v>
+        <v>85.37</v>
       </c>
       <c r="G5">
-        <v>12.2</v>
+        <v>14.63</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -4397,27 +4397,27 @@
         <v>36</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6">
         <v>87.8</v>
       </c>
       <c r="G6">
+        <v>12.2</v>
+      </c>
+      <c r="H6">
+        <v>7.2</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="H6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
       <c r="J6">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -4426,25 +4426,25 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>90.23999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="G7">
-        <v>9.76</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>12.2</v>
       </c>
     </row>
   </sheetData>
@@ -4518,7 +4518,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4558,7 +4558,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4758,7 +4758,7 @@
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4838,7 +4838,7 @@
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -5576,7 +5576,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5608,39 +5608,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920236</v>
+        <v>22330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5649,50 +5649,50 @@
         <v>64</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920366</v>
+        <v>22330051920231</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920366</v>
+        <v>22330051920232</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5700,22 +5700,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920231</v>
+        <v>22330051920233</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5723,16 +5723,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920232</v>
+        <v>22330051920243</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -5741,98 +5741,52 @@
         <v>63</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920233</v>
+        <v>22330051920368</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920243</v>
+        <v>22330051920256</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="D9" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920368</v>
-      </c>
-      <c r="B10" t="s">
-        <v>127</v>
-      </c>
-      <c r="C10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D10" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920256</v>
-      </c>
-      <c r="B11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" t="s">
-        <v>180</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="183">
   <si>
     <t>Materia</t>
   </si>
@@ -1381,7 +1381,7 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -1417,7 +1417,7 @@
         <v>6</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V8">
         <v>6</v>
@@ -2767,7 +2767,7 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -2803,7 +2803,7 @@
         <v>7</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2998,7 +2998,7 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>9</v>
@@ -3034,7 +3034,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -4298,19 +4298,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>78.05</v>
+        <v>75.61</v>
       </c>
       <c r="G3">
-        <v>2.44</v>
+        <v>4.88</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>8</v>
@@ -5576,7 +5576,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5608,22 +5608,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920366</v>
+        <v>22330051920233</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5631,22 +5631,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920366</v>
+        <v>22330051920233</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5654,45 +5654,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920231</v>
+        <v>22330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920232</v>
+        <v>22330051920366</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5700,16 +5700,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920233</v>
+        <v>22330051920231</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -5723,16 +5723,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920243</v>
+        <v>22330051920232</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>161</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -5741,27 +5741,27 @@
         <v>63</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920368</v>
+        <v>22330051920243</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
         <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5769,16 +5769,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920256</v>
+        <v>22330051920368</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>
@@ -5787,6 +5787,29 @@
         <v>62</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920256</v>
+      </c>
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -1070,7 +1070,7 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1085,7 +1085,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1147,7 +1147,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -1162,7 +1162,7 @@
         <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1183,7 +1183,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1224,7 +1224,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -1239,7 +1239,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1301,7 +1301,7 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1378,7 +1378,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I8">
         <v>5</v>
@@ -1393,7 +1393,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1414,7 +1414,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -1455,7 +1455,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>7</v>
@@ -1470,7 +1470,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1491,7 +1491,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>8</v>
@@ -1506,7 +1506,7 @@
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1532,7 +1532,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -1547,7 +1547,7 @@
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1583,7 +1583,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1609,7 +1609,7 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1624,7 +1624,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1645,7 +1645,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1686,7 +1686,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I12">
         <v>6</v>
@@ -1701,7 +1701,7 @@
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1722,7 +1722,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -1763,7 +1763,7 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>7</v>
@@ -1778,7 +1778,7 @@
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1799,7 +1799,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1855,7 +1855,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1891,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -1932,7 +1932,7 @@
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1994,7 +1994,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -2009,7 +2009,7 @@
         <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2030,7 +2030,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>6</v>
@@ -2071,7 +2071,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>10</v>
@@ -2086,7 +2086,7 @@
         <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2148,7 +2148,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -2163,7 +2163,7 @@
         <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2184,7 +2184,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2225,7 +2225,7 @@
         <v>-1</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2302,7 +2302,7 @@
         <v>-1</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2379,7 +2379,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -2394,7 +2394,7 @@
         <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2415,7 +2415,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>5</v>
@@ -2456,7 +2456,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>7</v>
@@ -2471,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2492,7 +2492,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2533,7 +2533,7 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>7</v>
@@ -2548,7 +2548,7 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2569,7 +2569,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23">
         <v>7</v>
@@ -2584,7 +2584,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2610,7 +2610,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>6</v>
@@ -2625,7 +2625,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2646,7 +2646,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>6</v>
@@ -2687,7 +2687,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>7</v>
@@ -2702,7 +2702,7 @@
         <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2723,7 +2723,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2738,7 +2738,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2764,7 +2764,7 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I26">
         <v>5</v>
@@ -2779,7 +2779,7 @@
         <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2815,7 +2815,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2841,7 +2841,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>6</v>
@@ -2856,7 +2856,7 @@
         <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2877,7 +2877,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2918,7 +2918,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>6</v>
@@ -2933,7 +2933,7 @@
         <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2954,7 +2954,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>6</v>
@@ -2969,7 +2969,7 @@
         <v>8</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2995,7 +2995,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>5</v>
@@ -3010,7 +3010,7 @@
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3072,7 +3072,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -3087,7 +3087,7 @@
         <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3149,7 +3149,7 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -3164,7 +3164,7 @@
         <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3185,7 +3185,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -3226,7 +3226,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I32">
         <v>6</v>
@@ -3241,7 +3241,7 @@
         <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3303,7 +3303,7 @@
         <v>5</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3318,7 +3318,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3380,7 +3380,7 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I34">
         <v>10</v>
@@ -3395,7 +3395,7 @@
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3416,7 +3416,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>10</v>
@@ -3431,7 +3431,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3457,7 +3457,7 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I35">
         <v>8</v>
@@ -3472,7 +3472,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3508,7 +3508,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3534,7 +3534,7 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>6</v>
@@ -3549,7 +3549,7 @@
         <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3585,7 +3585,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3611,7 +3611,7 @@
         <v>-1</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>6</v>
@@ -3688,7 +3688,7 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
         <v>10</v>
@@ -3703,7 +3703,7 @@
         <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3724,7 +3724,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U38">
         <v>9</v>
@@ -3765,7 +3765,7 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
         <v>6</v>
@@ -3780,7 +3780,7 @@
         <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3801,7 +3801,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>7</v>
@@ -3816,7 +3816,7 @@
         <v>10</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3857,7 +3857,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3919,7 +3919,7 @@
         <v>6</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I41">
         <v>6</v>
@@ -3934,7 +3934,7 @@
         <v>9</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3996,7 +3996,7 @@
         <v>6</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>7</v>
@@ -4011,7 +4011,7 @@
         <v>9</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4073,7 +4073,7 @@
         <v>6</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>8</v>
@@ -4088,7 +4088,7 @@
         <v>9</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4124,7 +4124,7 @@
         <v>9</v>
       </c>
       <c r="Y43">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4150,7 +4150,7 @@
         <v>6</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I44">
         <v>7</v>
@@ -4165,7 +4165,7 @@
         <v>10</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4266,16 +4266,16 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>75.61</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="G2">
-        <v>19.51</v>
+        <v>29.27</v>
       </c>
       <c r="H2">
         <v>6.4</v>
@@ -4330,16 +4330,16 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>80.48999999999999</v>
+        <v>78.05</v>
       </c>
       <c r="G4">
-        <v>12.2</v>
+        <v>14.63</v>
       </c>
       <c r="H4">
         <v>6.6</v>
@@ -5608,22 +5608,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920233</v>
+        <v>22330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5631,22 +5631,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920233</v>
+        <v>22330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5654,45 +5654,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920366</v>
+        <v>22330051920231</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920366</v>
+        <v>22330051920232</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5700,48 +5700,48 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920231</v>
+        <v>22330051920238</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920232</v>
+        <v>22330051920242</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5769,16 +5769,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920368</v>
+        <v>22330051920369</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="D9" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
         <v>5</v>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="183">
   <si>
     <t>Materia</t>
   </si>
@@ -236,52 +236,175 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>SOBRINO</t>
+  </si>
+  <si>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>ALDO EMANUEL</t>
+  </si>
+  <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
+    <t>KARLOS ARATH</t>
+  </si>
+  <si>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
+    <t>BRANDON ADALID</t>
+  </si>
+  <si>
     <t>AJACTLE</t>
   </si>
   <si>
-    <t>ARELLANO</t>
+    <t>ANGELES</t>
   </si>
   <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>BONILLA</t>
+    <t>CANUTO</t>
   </si>
   <si>
     <t>DECTOR</t>
   </si>
   <si>
-    <t>GALICIA</t>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GAYTAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ORTEGA</t>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MARES</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>SOBRINO</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>FIERROS</t>
+    <t>ROCHA</t>
   </si>
   <si>
     <t>ESTRADA</t>
   </si>
   <si>
-    <t>IBAÑEZ</t>
+    <t>MEDINA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
   </si>
   <si>
     <t>ALDUZIN</t>
@@ -290,31 +413,85 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
+    <t>APOLINAR</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>GROT</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GARNICA</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>RUBI</t>
   </si>
   <si>
-    <t>ALDO EMANUEL</t>
+    <t>AZURA</t>
   </si>
   <si>
     <t>VANNYA</t>
   </si>
   <si>
-    <t>FERNANDA MARGARITA</t>
+    <t>ANA SHECIT</t>
   </si>
   <si>
     <t>KEVIN ALEXIS</t>
   </si>
   <si>
-    <t>KARLOS ARATH</t>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>JOSAVIA ARIDAI</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
   </si>
   <si>
     <t>ANDRICK YAEL</t>
@@ -323,232 +500,55 @@
     <t>JARET</t>
   </si>
   <si>
-    <t>JOSE ALDAIR</t>
+    <t>MARIA ANGELES</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>BRENDA</t>
+  </si>
+  <si>
+    <t>LUISA MARIA</t>
+  </si>
+  <si>
+    <t>LILIAN</t>
+  </si>
+  <si>
+    <t>JULIO ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE ALBIN</t>
+  </si>
+  <si>
+    <t>ATZIN LUCERO</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
+    <t>JOSE JAVIER</t>
+  </si>
+  <si>
+    <t>NOEMI DEL ROCIO</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
   </si>
   <si>
     <t>AILYN</t>
-  </si>
-  <si>
-    <t>BRANDON ADALID</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>APOLINAR</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>AZURA</t>
-  </si>
-  <si>
-    <t>ANA SHECIT</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>MARIA ANGELES</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>ARACELI</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>LILIAN</t>
-  </si>
-  <si>
-    <t>JULIO ANTONIO</t>
-  </si>
-  <si>
-    <t>JOSE ALBIN</t>
-  </si>
-  <si>
-    <t>ATZIN LUCERO</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>JOSE JAVIER</t>
-  </si>
-  <si>
-    <t>NOEMI DEL ROCIO</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
   </si>
   <si>
     <t>HAZEL</t>
@@ -1055,7 +1055,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -1073,7 +1073,7 @@
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1109,7 +1109,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -1286,7 +1286,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>8</v>
@@ -1304,7 +1304,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>8</v>
@@ -1340,7 +1340,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1594,7 +1594,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>6</v>
@@ -1612,7 +1612,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1648,7 +1648,7 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1822,10 +1822,10 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -1840,10 +1840,10 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -1876,10 +1876,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -2210,7 +2210,7 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -2222,13 +2222,13 @@
         <v>7</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -2240,7 +2240,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2264,7 +2264,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2276,7 +2276,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2287,7 +2287,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2299,13 +2299,13 @@
         <v>7</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H20">
         <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>9</v>
@@ -2317,7 +2317,7 @@
         <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2341,7 +2341,7 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2353,7 +2353,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -3288,7 +3288,7 @@
         <v>5</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -3306,7 +3306,7 @@
         <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J33">
         <v>4</v>
@@ -3342,7 +3342,7 @@
         <v>5</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
         <v>5</v>
@@ -3608,7 +3608,7 @@
         <v>8</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H37">
         <v>5</v>
@@ -3626,7 +3626,7 @@
         <v>9</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3662,7 +3662,7 @@
         <v>9</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3824,10 +3824,10 @@
         <v>48</v>
       </c>
       <c r="B40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -3842,10 +3842,10 @@
         <v>5</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J40">
         <v>4</v>
@@ -3878,10 +3878,10 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V40">
         <v>5</v>
@@ -4269,22 +4269,22 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2">
         <v>65.84999999999999</v>
       </c>
       <c r="G2">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4298,25 +4298,25 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>75.61</v>
+        <v>78.05</v>
       </c>
       <c r="G3">
-        <v>4.88</v>
+        <v>21.95</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>19.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4330,25 +4330,25 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>78.05</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G4">
-        <v>14.63</v>
+        <v>17.07</v>
       </c>
       <c r="H4">
         <v>6.6</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>7.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4454,7 +4454,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4483,36 +4483,36 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>22330051920396</v>
+        <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
       </c>
       <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
         <v>82</v>
       </c>
-      <c r="D2" t="s">
-        <v>93</v>
-      </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920231</v>
+        <v>22330051920233</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
       </c>
       <c r="C3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s">
         <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4523,36 +4523,36 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920232</v>
+        <v>22330051920422</v>
       </c>
       <c r="B4" t="s">
         <v>74</v>
       </c>
       <c r="C4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" t="s">
         <v>84</v>
       </c>
-      <c r="D4" t="s">
-        <v>95</v>
-      </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920233</v>
+        <v>22330051920376</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
         <v>85</v>
-      </c>
-      <c r="D5" t="s">
-        <v>96</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -4563,281 +4563,21 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920236</v>
+        <v>22330051920255</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
       </c>
       <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
         <v>86</v>
       </c>
-      <c r="D6" t="s">
-        <v>97</v>
-      </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920422</v>
-      </c>
-      <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920422</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920422</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>98</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920398</v>
-      </c>
-      <c r="B10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920398</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920357</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920357</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920376</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920376</v>
-      </c>
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920366</v>
-      </c>
-      <c r="B16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920255</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920255</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920255</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>92</v>
-      </c>
-      <c r="D19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4874,87 +4614,87 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920422</v>
+        <v>22330051920231</v>
       </c>
       <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
         <v>77</v>
       </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920255</v>
+        <v>22330051920233</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920398</v>
+        <v>22330051920422</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920357</v>
+        <v>22330051920376</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920376</v>
+        <v>22330051920255</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4962,33 +4702,33 @@
         <v>22330051920396</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920231</v>
+        <v>22330051920230</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4996,33 +4736,33 @@
         <v>22330051920232</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920233</v>
+        <v>22330051920234</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5030,44 +4770,44 @@
         <v>22330051920236</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920366</v>
+        <v>22330051920237</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920230</v>
+        <v>22330051920238</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
         <v>153</v>
@@ -5078,13 +4818,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920234</v>
+        <v>22330051920239</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D14" t="s">
         <v>154</v>
@@ -5095,13 +4835,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920237</v>
+        <v>22330051920240</v>
       </c>
       <c r="B15" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
         <v>155</v>
@@ -5112,13 +4852,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920238</v>
+        <v>22330051920241</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
         <v>156</v>
@@ -5129,13 +4869,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920239</v>
+        <v>22330051920242</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D17" t="s">
         <v>157</v>
@@ -5146,13 +4886,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920240</v>
+        <v>22330051920398</v>
       </c>
       <c r="B18" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D18" t="s">
         <v>158</v>
@@ -5163,13 +4903,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920241</v>
+        <v>22330051920357</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
         <v>159</v>
@@ -5180,13 +4920,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920242</v>
+        <v>22330051920243</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="D20" t="s">
         <v>160</v>
@@ -5197,13 +4937,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920243</v>
+        <v>22330051920245</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D21" t="s">
         <v>161</v>
@@ -5214,13 +4954,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920245</v>
+        <v>22330051920369</v>
       </c>
       <c r="B22" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
         <v>162</v>
@@ -5231,13 +4971,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920369</v>
+        <v>22330051920318</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
         <v>163</v>
@@ -5248,13 +4988,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920318</v>
+        <v>22330051920319</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
         <v>164</v>
@@ -5265,13 +5005,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920319</v>
+        <v>22330051920246</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
         <v>165</v>
@@ -5282,13 +5022,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920246</v>
+        <v>22330051920249</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
         <v>166</v>
@@ -5299,13 +5039,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920249</v>
+        <v>22330051920414</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
         <v>167</v>
@@ -5316,13 +5056,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920414</v>
+        <v>22330051920248</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="D28" t="s">
         <v>168</v>
@@ -5333,13 +5073,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920248</v>
+        <v>22330051920250</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="D29" t="s">
         <v>169</v>
@@ -5350,13 +5090,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920250</v>
+        <v>22330051920251</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
         <v>170</v>
@@ -5367,13 +5107,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920251</v>
+        <v>22330051920399</v>
       </c>
       <c r="B31" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C31" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D31" t="s">
         <v>171</v>
@@ -5384,13 +5124,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920399</v>
+        <v>22330051920400</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C32" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D32" t="s">
         <v>172</v>
@@ -5401,13 +5141,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920400</v>
+        <v>22330051920252</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
         <v>173</v>
@@ -5418,13 +5158,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920252</v>
+        <v>22330051920253</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="D34" t="s">
         <v>174</v>
@@ -5435,13 +5175,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920253</v>
+        <v>22330051920235</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C35" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
         <v>175</v>
@@ -5452,13 +5192,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920235</v>
+        <v>22330051920366</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C36" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D36" t="s">
         <v>176</v>
@@ -5472,10 +5212,10 @@
         <v>22330051920368</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
         <v>177</v>
@@ -5489,10 +5229,10 @@
         <v>22330051920254</v>
       </c>
       <c r="B38" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D38" t="s">
         <v>178</v>
@@ -5506,10 +5246,10 @@
         <v>22330051920257</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C39" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D39" t="s">
         <v>179</v>
@@ -5523,10 +5263,10 @@
         <v>22330051920256</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C40" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D40" t="s">
         <v>180</v>
@@ -5540,10 +5280,10 @@
         <v>22330051920401</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C41" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D41" t="s">
         <v>181</v>
@@ -5557,10 +5297,10 @@
         <v>22330051920259</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D42" t="s">
         <v>182</v>
@@ -5576,7 +5316,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5611,13 +5351,13 @@
         <v>22330051920366</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5634,13 +5374,13 @@
         <v>22330051920366</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5649,7 +5389,7 @@
         <v>64</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5657,13 +5397,13 @@
         <v>22330051920231</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -5680,13 +5420,13 @@
         <v>22330051920232</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -5695,7 +5435,7 @@
         <v>63</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -5703,13 +5443,13 @@
         <v>22330051920238</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5726,13 +5466,13 @@
         <v>22330051920242</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
@@ -5746,22 +5486,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920243</v>
+        <v>22330051920357</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5769,22 +5509,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920369</v>
+        <v>22330051920243</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5792,16 +5532,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920256</v>
+        <v>22330051920369</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5810,6 +5550,29 @@
         <v>62</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920256</v>
+      </c>
+      <c r="B11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -1461,7 +1461,7 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>7</v>
@@ -1497,7 +1497,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>8</v>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="183">
   <si>
     <t>Materia</t>
   </si>
@@ -212,13 +212,13 @@
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
     <t>Loyo Sanchez Raul Manuel</t>
@@ -1094,7 +1094,7 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -1171,7 +1171,7 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1248,7 +1248,7 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1325,7 +1325,7 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>7</v>
@@ -1402,7 +1402,7 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1420,7 +1420,7 @@
         <v>5</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1479,7 +1479,7 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1497,7 +1497,7 @@
         <v>8</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1556,7 +1556,7 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1633,7 +1633,7 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1710,7 +1710,7 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1728,7 +1728,7 @@
         <v>6</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1787,7 +1787,7 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1864,7 +1864,7 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1941,7 +1941,7 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -2018,7 +2018,7 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2036,7 +2036,7 @@
         <v>6</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -2095,7 +2095,7 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2172,7 +2172,7 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2249,7 +2249,7 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -2326,7 +2326,7 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2344,7 +2344,7 @@
         <v>6</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2403,7 +2403,7 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2480,7 +2480,7 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2557,7 +2557,7 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2575,7 +2575,7 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>7</v>
@@ -2634,7 +2634,7 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2652,7 +2652,7 @@
         <v>6</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2711,7 +2711,7 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2788,7 +2788,7 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2806,7 +2806,7 @@
         <v>6</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2865,7 +2865,7 @@
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2942,7 +2942,7 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -3019,7 +3019,7 @@
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3037,7 +3037,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>10</v>
@@ -3096,7 +3096,7 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3114,7 +3114,7 @@
         <v>7</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3173,7 +3173,7 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3191,7 +3191,7 @@
         <v>8</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3250,7 +3250,7 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3327,7 +3327,7 @@
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3404,7 +3404,7 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3422,7 +3422,7 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3481,7 +3481,7 @@
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3558,7 +3558,7 @@
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3576,7 +3576,7 @@
         <v>6</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3635,7 +3635,7 @@
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3653,7 +3653,7 @@
         <v>6</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>7</v>
@@ -3712,7 +3712,7 @@
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3730,7 +3730,7 @@
         <v>9</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>8</v>
@@ -3789,7 +3789,7 @@
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3866,7 +3866,7 @@
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3943,7 +3943,7 @@
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q41">
         <v>-1</v>
@@ -3961,7 +3961,7 @@
         <v>6</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W41">
         <v>6</v>
@@ -4020,7 +4020,7 @@
         <v>-1</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q42">
         <v>-1</v>
@@ -4097,7 +4097,7 @@
         <v>-1</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q43">
         <v>-1</v>
@@ -4115,7 +4115,7 @@
         <v>9</v>
       </c>
       <c r="V43">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W43">
         <v>10</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q44">
         <v>-1</v>
@@ -4192,7 +4192,7 @@
         <v>7</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W44">
         <v>8</v>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -4342,7 +4342,7 @@
         <v>17.07</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -4362,19 +4362,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>85.37</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G5">
-        <v>14.63</v>
+        <v>17.07</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -4394,19 +4394,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>87.8</v>
+        <v>85.37</v>
       </c>
       <c r="G6">
-        <v>12.2</v>
+        <v>14.63</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5316,7 +5316,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5348,16 +5348,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920366</v>
+        <v>22330051920369</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5371,19 +5371,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920366</v>
+        <v>22330051920369</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>64</v>
@@ -5394,45 +5394,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920231</v>
+        <v>22330051920366</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920232</v>
+        <v>22330051920366</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5440,45 +5440,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920238</v>
+        <v>22330051920231</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920242</v>
+        <v>22330051920232</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5486,16 +5486,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920357</v>
+        <v>22330051920238</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920243</v>
+        <v>22330051920242</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5532,16 +5532,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920369</v>
+        <v>22330051920357</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5555,24 +5555,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
+        <v>22330051920243</v>
+      </c>
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
         <v>22330051920256</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>118</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>144</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>180</v>
       </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
         <v>62</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="183">
   <si>
     <t>Materia</t>
   </si>
@@ -218,10 +218,10 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Loyo Sanchez Raul Manuel</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Loyo Sanchez Raul Manuel</t>
   </si>
   <si>
     <t>NC</t>
@@ -1097,7 +1097,7 @@
         <v>4</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1115,7 +1115,7 @@
         <v>5</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>8</v>
@@ -1174,7 +1174,7 @@
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1192,7 +1192,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1251,7 +1251,7 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1269,7 +1269,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>-1</v>
@@ -1328,7 +1328,7 @@
         <v>4</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1405,7 +1405,7 @@
         <v>4</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1423,7 +1423,7 @@
         <v>5</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>-1</v>
@@ -1482,7 +1482,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1500,7 +1500,7 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1636,7 +1636,7 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1654,7 +1654,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1713,7 +1713,7 @@
         <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1790,7 +1790,7 @@
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1867,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1885,7 +1885,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X14">
         <v>-1</v>
@@ -1944,7 +1944,7 @@
         <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1962,7 +1962,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -2021,7 +2021,7 @@
         <v>4</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2039,7 +2039,7 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -2098,7 +2098,7 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2175,7 +2175,7 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2252,7 +2252,7 @@
         <v>4</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2270,7 +2270,7 @@
         <v>5</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2329,7 +2329,7 @@
         <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2347,7 +2347,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2406,7 +2406,7 @@
         <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2483,7 +2483,7 @@
         <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2560,7 +2560,7 @@
         <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2637,7 +2637,7 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2655,7 +2655,7 @@
         <v>6</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2714,7 +2714,7 @@
         <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2791,7 +2791,7 @@
         <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2809,7 +2809,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2868,7 +2868,7 @@
         <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2945,7 +2945,7 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2963,7 +2963,7 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -3022,7 +3022,7 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3099,7 +3099,7 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3176,7 +3176,7 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3194,7 +3194,7 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3253,7 +3253,7 @@
         <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3271,7 +3271,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -3330,7 +3330,7 @@
         <v>4</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3407,7 +3407,7 @@
         <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3425,7 +3425,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>9</v>
@@ -3484,7 +3484,7 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3561,7 +3561,7 @@
         <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3579,7 +3579,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>9</v>
@@ -3638,7 +3638,7 @@
         <v>4</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3715,7 +3715,7 @@
         <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3792,7 +3792,7 @@
         <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3869,7 +3869,7 @@
         <v>4</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3946,7 +3946,7 @@
         <v>4</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -3964,7 +3964,7 @@
         <v>6</v>
       </c>
       <c r="W41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X41">
         <v>9</v>
@@ -4023,7 +4023,7 @@
         <v>7</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -4100,7 +4100,7 @@
         <v>5</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -4177,7 +4177,7 @@
         <v>7</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R44">
         <v>-1</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -4394,30 +4394,30 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>85.37</v>
+        <v>87.8</v>
       </c>
       <c r="G6">
-        <v>14.63</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -4426,25 +4426,25 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>95.12</v>
+      </c>
+      <c r="G7">
+        <v>4.88</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>87.8</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>12.2</v>
       </c>
     </row>
   </sheetData>
@@ -4498,7 +4498,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4518,7 +4518,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4538,7 +4538,7 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4558,7 +4558,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4578,7 +4578,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -5316,7 +5316,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5348,16 +5348,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920369</v>
+        <v>22330051920239</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5371,22 +5371,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920369</v>
+        <v>22330051920239</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5394,16 +5394,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920366</v>
+        <v>22330051920369</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5417,22 +5417,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920366</v>
+        <v>22330051920369</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5440,45 +5440,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920231</v>
+        <v>22330051920366</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920232</v>
+        <v>22330051920366</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5486,45 +5486,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920238</v>
+        <v>22330051920231</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920242</v>
+        <v>22330051920232</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5532,16 +5532,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920357</v>
+        <v>22330051920238</v>
       </c>
       <c r="B10" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920243</v>
+        <v>22330051920242</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="D11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5578,16 +5578,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920256</v>
+        <v>22330051920357</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -5596,6 +5596,52 @@
         <v>62</v>
       </c>
       <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920243</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920256</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" t="s">
+        <v>180</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -101,7 +101,7 @@
     <t>GONZALEZ MENDEZ JOCELYN</t>
   </si>
   <si>
-    <t>HERNANDEZ ALDUZIN ANDRICK YAEL</t>
+    <t>HERNANDEZ ALDUCIN ANDRICK YAEL</t>
   </si>
   <si>
     <t>HERNANDEZ GUTIERREZ JARET</t>
@@ -407,7 +407,7 @@
     <t>MENDEZ</t>
   </si>
   <si>
-    <t>ALDUZIN</t>
+    <t>ALDUCIN</t>
   </si>
   <si>
     <t>GUTIERREZ</t>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="183">
   <si>
     <t>Materia</t>
   </si>
@@ -1091,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>4</v>
@@ -1100,10 +1100,10 @@
         <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -1168,7 +1168,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>7</v>
@@ -1177,16 +1177,16 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>7</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -1245,7 +1245,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>8</v>
@@ -1257,13 +1257,13 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>6</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -1322,7 +1322,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>4</v>
@@ -1331,10 +1331,10 @@
         <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>6</v>
@@ -1352,7 +1352,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1399,7 +1399,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>4</v>
@@ -1411,13 +1411,13 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>5</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>5</v>
@@ -1429,7 +1429,7 @@
         <v>-1</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1476,7 +1476,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>8</v>
@@ -1485,10 +1485,10 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1553,7 +1553,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>8</v>
@@ -1562,10 +1562,10 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1580,10 +1580,10 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>7</v>
@@ -1639,10 +1639,10 @@
         <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>5</v>
@@ -1660,7 +1660,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1707,7 +1707,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -1716,16 +1716,16 @@
         <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>6</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1784,7 +1784,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>7</v>
@@ -1793,10 +1793,10 @@
         <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>5</v>
@@ -1811,7 +1811,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1861,7 +1861,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
         <v>4</v>
@@ -1873,7 +1873,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>5</v>
@@ -1891,7 +1891,7 @@
         <v>-1</v>
       </c>
       <c r="Y14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1938,7 +1938,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -1947,16 +1947,16 @@
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>5</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>6</v>
@@ -2015,7 +2015,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>4</v>
@@ -2024,10 +2024,10 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -2092,7 +2092,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>8</v>
@@ -2101,10 +2101,10 @@
         <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>6</v>
@@ -2169,7 +2169,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>7</v>
@@ -2178,16 +2178,16 @@
         <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>5</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V18">
         <v>7</v>
@@ -2246,7 +2246,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>4</v>
@@ -2255,10 +2255,10 @@
         <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>5</v>
@@ -2323,7 +2323,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>6</v>
@@ -2332,16 +2332,16 @@
         <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>5</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2400,7 +2400,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>8</v>
@@ -2409,16 +2409,16 @@
         <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2430,7 +2430,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2477,7 +2477,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>9</v>
@@ -2486,10 +2486,10 @@
         <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2507,7 +2507,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2554,7 +2554,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
         <v>5</v>
@@ -2563,16 +2563,16 @@
         <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T23">
         <v>5</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2631,7 +2631,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>5</v>
@@ -2640,10 +2640,10 @@
         <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2708,7 +2708,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>8</v>
@@ -2717,10 +2717,10 @@
         <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2785,7 +2785,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>6</v>
@@ -2794,16 +2794,16 @@
         <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>7</v>
       </c>
       <c r="U26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>7</v>
@@ -2815,7 +2815,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2862,7 +2862,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>9</v>
@@ -2871,16 +2871,16 @@
         <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>9</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>8</v>
@@ -2939,7 +2939,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>8</v>
@@ -2948,16 +2948,16 @@
         <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>7</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2966,7 +2966,7 @@
         <v>8</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -3016,7 +3016,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
         <v>7</v>
@@ -3025,16 +3025,16 @@
         <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>7</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -3046,7 +3046,7 @@
         <v>10</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3093,7 +3093,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
         <v>9</v>
@@ -3102,10 +3102,10 @@
         <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -3170,7 +3170,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
         <v>5</v>
@@ -3179,16 +3179,16 @@
         <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
         <v>8</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>6</v>
@@ -3197,10 +3197,10 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3247,7 +3247,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>7</v>
@@ -3256,10 +3256,10 @@
         <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>6</v>
@@ -3324,7 +3324,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>4</v>
@@ -3336,7 +3336,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
         <v>5</v>
@@ -3401,7 +3401,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>6</v>
@@ -3410,16 +3410,16 @@
         <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>7</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3478,7 +3478,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>8</v>
@@ -3487,10 +3487,10 @@
         <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>8</v>
@@ -3555,7 +3555,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>6</v>
@@ -3564,10 +3564,10 @@
         <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>6</v>
@@ -3632,7 +3632,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
         <v>4</v>
@@ -3641,16 +3641,16 @@
         <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>5</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V37">
         <v>6</v>
@@ -3662,7 +3662,7 @@
         <v>9</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3709,7 +3709,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
         <v>8</v>
@@ -3718,10 +3718,10 @@
         <v>8</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>6</v>
@@ -3786,7 +3786,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P39">
         <v>9</v>
@@ -3795,10 +3795,10 @@
         <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>8</v>
@@ -3863,7 +3863,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P40">
         <v>4</v>
@@ -3875,7 +3875,7 @@
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T40">
         <v>5</v>
@@ -3940,7 +3940,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P41">
         <v>4</v>
@@ -3949,10 +3949,10 @@
         <v>9</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T41">
         <v>5</v>
@@ -4017,7 +4017,7 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P42">
         <v>7</v>
@@ -4026,16 +4026,16 @@
         <v>9</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T42">
         <v>7</v>
       </c>
       <c r="U42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V42">
         <v>7</v>
@@ -4094,7 +4094,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P43">
         <v>5</v>
@@ -4103,10 +4103,10 @@
         <v>10</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T43">
         <v>6</v>
@@ -4124,7 +4124,7 @@
         <v>9</v>
       </c>
       <c r="Y43">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4171,7 +4171,7 @@
         <v>-1</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P44">
         <v>7</v>
@@ -4180,16 +4180,16 @@
         <v>9</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T44">
         <v>7</v>
       </c>
       <c r="U44">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V44">
         <v>8</v>
@@ -4298,19 +4298,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>78.05</v>
+        <v>70.73</v>
       </c>
       <c r="G3">
-        <v>21.95</v>
+        <v>29.27</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4362,16 +4362,16 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>82.93000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="G5">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
       <c r="H5">
         <v>6.6</v>
@@ -5316,7 +5316,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5348,16 +5348,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920239</v>
+        <v>22330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5371,22 +5371,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920239</v>
+        <v>22330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5394,16 +5394,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920369</v>
+        <v>22330051920239</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5417,22 +5417,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920369</v>
+        <v>22330051920239</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5440,16 +5440,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920366</v>
+        <v>22330051920242</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5463,22 +5463,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920366</v>
+        <v>22330051920242</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D7" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5486,39 +5486,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920231</v>
+        <v>22330051920366</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920232</v>
+        <v>22330051920366</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5532,45 +5532,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920238</v>
+        <v>22330051920231</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920242</v>
+        <v>22330051920232</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5578,22 +5578,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920357</v>
+        <v>22330051920237</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5601,22 +5601,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920243</v>
+        <v>22330051920238</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5624,16 +5624,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920256</v>
+        <v>22330051920357</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D14" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
@@ -5642,6 +5642,52 @@
         <v>62</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920400</v>
+      </c>
+      <c r="B15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>63</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920256</v>
+      </c>
+      <c r="B16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="183">
   <si>
     <t>Materia</t>
   </si>
@@ -206,19 +206,19 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Loyo Sanchez Raul Manuel</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Loyo Sanchez Raul Manuel</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
@@ -1088,7 +1088,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>5</v>
@@ -1106,7 +1106,7 @@
         <v>5</v>
       </c>
       <c r="T4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -1165,7 +1165,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -1183,7 +1183,7 @@
         <v>6</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -1319,7 +1319,7 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -1337,7 +1337,7 @@
         <v>6</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1396,7 +1396,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O8">
         <v>7</v>
@@ -1414,7 +1414,7 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8">
         <v>6</v>
@@ -1473,7 +1473,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1550,7 +1550,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>7</v>
@@ -1568,7 +1568,7 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1627,7 +1627,7 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>7</v>
@@ -1645,7 +1645,7 @@
         <v>8</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>5</v>
@@ -1704,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>5</v>
@@ -1781,7 +1781,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>9</v>
@@ -1799,7 +1799,7 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1858,7 +1858,7 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -1876,7 +1876,7 @@
         <v>7</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -1935,7 +1935,7 @@
         <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>5</v>
@@ -1953,7 +1953,7 @@
         <v>5</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -2012,7 +2012,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -2089,7 +2089,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -2107,7 +2107,7 @@
         <v>8</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>10</v>
@@ -2166,7 +2166,7 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>8</v>
@@ -2184,7 +2184,7 @@
         <v>7</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2243,7 +2243,7 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>5</v>
@@ -2320,7 +2320,7 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>8</v>
@@ -2338,7 +2338,7 @@
         <v>6</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2397,7 +2397,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>7</v>
@@ -2474,7 +2474,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>8</v>
@@ -2551,7 +2551,7 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>5</v>
@@ -2569,7 +2569,7 @@
         <v>6</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>5</v>
@@ -2628,7 +2628,7 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2705,7 +2705,7 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>7</v>
@@ -2782,7 +2782,7 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>10</v>
@@ -2859,7 +2859,7 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>8</v>
@@ -2877,7 +2877,7 @@
         <v>8</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -2936,7 +2936,7 @@
         <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>8</v>
@@ -3013,7 +3013,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>10</v>
@@ -3090,7 +3090,7 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>7</v>
@@ -3108,7 +3108,7 @@
         <v>8</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>7</v>
@@ -3167,7 +3167,7 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>5</v>
@@ -3244,7 +3244,7 @@
         <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -3321,7 +3321,7 @@
         <v>5</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
         <v>5</v>
@@ -3398,7 +3398,7 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>10</v>
@@ -3416,7 +3416,7 @@
         <v>9</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>5</v>
@@ -3475,7 +3475,7 @@
         <v>7</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>10</v>
@@ -3552,7 +3552,7 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3570,7 +3570,7 @@
         <v>7</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>6</v>
@@ -3629,7 +3629,7 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
         <v>5</v>
@@ -3647,7 +3647,7 @@
         <v>7</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>5</v>
@@ -3706,7 +3706,7 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>10</v>
@@ -3783,7 +3783,7 @@
         <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>7</v>
@@ -3801,7 +3801,7 @@
         <v>10</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U39">
         <v>7</v>
@@ -3860,7 +3860,7 @@
         <v>5</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O40">
         <v>5</v>
@@ -3937,7 +3937,7 @@
         <v>6</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>7</v>
@@ -3955,7 +3955,7 @@
         <v>6</v>
       </c>
       <c r="T41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U41">
         <v>6</v>
@@ -4014,7 +4014,7 @@
         <v>6</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -4091,7 +4091,7 @@
         <v>7</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O43">
         <v>9</v>
@@ -4109,7 +4109,7 @@
         <v>5</v>
       </c>
       <c r="T43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U43">
         <v>9</v>
@@ -4168,7 +4168,7 @@
         <v>6</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O44">
         <v>6</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -4266,19 +4266,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>65.84999999999999</v>
+        <v>70.73</v>
       </c>
       <c r="G2">
-        <v>34.15</v>
+        <v>29.27</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -4298,19 +4298,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>70.73</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G3">
-        <v>29.27</v>
+        <v>17.07</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -4330,19 +4330,19 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>82.93000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="G4">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -4365,27 +4365,27 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>87.8</v>
       </c>
       <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
         <v>12.2</v>
-      </c>
-      <c r="H5">
-        <v>6.6</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -4394,25 +4394,25 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6">
+        <v>92.68000000000001</v>
+      </c>
+      <c r="G6">
+        <v>7.32</v>
+      </c>
+      <c r="H6">
+        <v>6.8</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>87.8</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>12.2</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4498,7 +4498,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4518,7 +4518,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4538,7 +4538,7 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4558,7 +4558,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4578,7 +4578,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -5316,7 +5316,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5348,19 +5348,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920236</v>
+        <v>22330051920369</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>62</v>
@@ -5371,19 +5371,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920236</v>
+        <v>22330051920369</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>63</v>
@@ -5394,45 +5394,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920239</v>
+        <v>22330051920231</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920239</v>
+        <v>22330051920232</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5440,19 +5440,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920242</v>
+        <v>22330051920236</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>62</v>
@@ -5463,22 +5463,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920242</v>
+        <v>22330051920237</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5486,22 +5486,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920366</v>
+        <v>22330051920239</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920366</v>
+        <v>22330051920242</v>
       </c>
       <c r="B9" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5532,162 +5532,47 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920231</v>
+        <v>22330051920400</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920232</v>
+        <v>22330051920366</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920237</v>
-      </c>
-      <c r="B12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" t="s">
-        <v>152</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920238</v>
-      </c>
-      <c r="B13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D13" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920357</v>
-      </c>
-      <c r="B14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" t="s">
-        <v>159</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920400</v>
-      </c>
-      <c r="B15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" t="s">
-        <v>139</v>
-      </c>
-      <c r="D15" t="s">
-        <v>172</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920256</v>
-      </c>
-      <c r="B16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" t="s">
-        <v>180</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1CV - Estadisticos 20221.xlsx
+++ b/grupos/1CV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="183">
   <si>
     <t>Materia</t>
   </si>
@@ -215,15 +215,15 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Loyo Sanchez Raul Manuel</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -236,325 +236,325 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>ANGELES</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
+    <t>DECTOR</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>FALFAN</t>
+  </si>
+  <si>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GALICIA</t>
   </si>
   <si>
+    <t>GAYTAN</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HIDALGO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LLAME</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MARES</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>PIÑA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>DE ROMAN</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>SOBRINO</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VALENTE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>FIERROS</t>
   </si>
   <si>
+    <t>ROCHA</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
     <t>IBAÑEZ</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>ALDUCIN</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>APOLINAR</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>PORTILLA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>GROT</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GARNICA</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>PULIDO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>RUBI</t>
+  </si>
+  <si>
     <t>ALDO EMANUEL</t>
   </si>
   <si>
+    <t>AZURA</t>
+  </si>
+  <si>
+    <t>VANNYA</t>
+  </si>
+  <si>
     <t>FERNANDA MARGARITA</t>
   </si>
   <si>
+    <t>ANA SHECIT</t>
+  </si>
+  <si>
+    <t>KEVIN ALEXIS</t>
+  </si>
+  <si>
+    <t>LUZ ALONDRA</t>
+  </si>
+  <si>
+    <t>JOSAVIA ARIDAI</t>
+  </si>
+  <si>
+    <t>CRHIS AMINADAB</t>
+  </si>
+  <si>
+    <t>AMALIA PAULINA</t>
+  </si>
+  <si>
     <t>KARLOS ARATH</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>ANDRICK YAEL</t>
+  </si>
+  <si>
+    <t>JARET</t>
+  </si>
+  <si>
+    <t>MARIA ANGELES</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>NIDIA GABRIELA</t>
+  </si>
+  <si>
+    <t>ARACELI</t>
+  </si>
+  <si>
+    <t>BRENDA</t>
+  </si>
+  <si>
+    <t>LUISA MARIA</t>
+  </si>
+  <si>
+    <t>LILIAN</t>
+  </si>
+  <si>
+    <t>JULIO ANTONIO</t>
+  </si>
+  <si>
+    <t>JOSE ALBIN</t>
+  </si>
+  <si>
+    <t>ATZIN LUCERO</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
     <t>JOSE ALDAIR</t>
   </si>
   <si>
+    <t>JULISSA MICHELLE</t>
+  </si>
+  <si>
+    <t>JOSE JAVIER</t>
+  </si>
+  <si>
+    <t>NOEMI DEL ROCIO</t>
+  </si>
+  <si>
+    <t>NATHALI</t>
+  </si>
+  <si>
+    <t>AILYN</t>
+  </si>
+  <si>
+    <t>HAZEL</t>
+  </si>
+  <si>
+    <t>KAREN ARLET</t>
+  </si>
+  <si>
     <t>BRANDON ADALID</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>ANGELES</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>DECTOR</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>FALFAN</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GAYTAN</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LLAME</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>MARES</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PIÑA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>DE ROMAN</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ROCHA</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>APOLINAR</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>GROT</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>RUBI</t>
-  </si>
-  <si>
-    <t>AZURA</t>
-  </si>
-  <si>
-    <t>VANNYA</t>
-  </si>
-  <si>
-    <t>ANA SHECIT</t>
-  </si>
-  <si>
-    <t>KEVIN ALEXIS</t>
-  </si>
-  <si>
-    <t>LUZ ALONDRA</t>
-  </si>
-  <si>
-    <t>JOSAVIA ARIDAI</t>
-  </si>
-  <si>
-    <t>CRHIS AMINADAB</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>ANDRICK YAEL</t>
-  </si>
-  <si>
-    <t>JARET</t>
-  </si>
-  <si>
-    <t>MARIA ANGELES</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>ARACELI</t>
-  </si>
-  <si>
-    <t>BRENDA</t>
-  </si>
-  <si>
-    <t>LUISA MARIA</t>
-  </si>
-  <si>
-    <t>LILIAN</t>
-  </si>
-  <si>
-    <t>JULIO ANTONIO</t>
-  </si>
-  <si>
-    <t>JOSE ALBIN</t>
-  </si>
-  <si>
-    <t>ATZIN LUCERO</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>JULISSA MICHELLE</t>
-  </si>
-  <si>
-    <t>JOSE JAVIER</t>
-  </si>
-  <si>
-    <t>NOEMI DEL ROCIO</t>
-  </si>
-  <si>
-    <t>NATHALI</t>
-  </si>
-  <si>
-    <t>AILYN</t>
-  </si>
-  <si>
-    <t>HAZEL</t>
-  </si>
-  <si>
-    <t>KAREN ARLET</t>
   </si>
   <si>
     <t>KAREN</t>
@@ -1218,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G6">
         <v>8</v>
@@ -1236,7 +1236,7 @@
         <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -1254,7 +1254,7 @@
         <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>8</v>
@@ -1272,7 +1272,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>8</v>
@@ -1372,7 +1372,7 @@
         <v>6</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>6</v>
@@ -1390,7 +1390,7 @@
         <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>6</v>
@@ -1408,7 +1408,7 @@
         <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>5</v>
@@ -1426,7 +1426,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1834,7 +1834,7 @@
         <v>6</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G14">
         <v>6</v>
@@ -1852,7 +1852,7 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -1870,7 +1870,7 @@
         <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>7</v>
@@ -1888,7 +1888,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -3297,7 +3297,7 @@
         <v>5</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -3315,7 +3315,7 @@
         <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>5</v>
@@ -3333,7 +3333,7 @@
         <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S33">
         <v>5</v>
@@ -3351,7 +3351,7 @@
         <v>5</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>5</v>
@@ -3836,7 +3836,7 @@
         <v>5</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -3854,7 +3854,7 @@
         <v>5</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>5</v>
@@ -3872,7 +3872,7 @@
         <v>5</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S40">
         <v>5</v>
@@ -3890,7 +3890,7 @@
         <v>5</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y40">
         <v>5</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -4362,30 +4362,30 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>87.8</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>7.32</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -4394,19 +4394,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>92.68000000000001</v>
+        <v>95.12</v>
       </c>
       <c r="G6">
-        <v>7.32</v>
+        <v>4.88</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4417,7 +4417,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -4438,7 +4438,7 @@
         <v>4.88</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4454,7 +4454,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4479,106 +4479,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920231</v>
-      </c>
-      <c r="B2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920233</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920422</v>
-      </c>
-      <c r="B4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920376</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920255</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4614,98 +4514,98 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920231</v>
+        <v>22330051920396</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920233</v>
+        <v>22330051920231</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920422</v>
+        <v>22330051920230</v>
       </c>
       <c r="B4" t="s">
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920376</v>
+        <v>22330051920232</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920255</v>
+        <v>22330051920233</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920396</v>
+        <v>22330051920234</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
         <v>147</v>
@@ -4716,13 +4616,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920230</v>
+        <v>22330051920236</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
         <v>148</v>
@@ -4733,13 +4633,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920232</v>
+        <v>22330051920237</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D9" t="s">
         <v>149</v>
@@ -4750,13 +4650,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920234</v>
+        <v>22330051920238</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
         <v>150</v>
@@ -4767,13 +4667,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920236</v>
+        <v>22330051920239</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
         <v>151</v>
@@ -4784,13 +4684,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920237</v>
+        <v>22330051920240</v>
       </c>
       <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
         <v>92</v>
-      </c>
-      <c r="C12" t="s">
-        <v>126</v>
       </c>
       <c r="D12" t="s">
         <v>152</v>
@@ -4801,13 +4701,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920238</v>
+        <v>22330051920422</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
         <v>153</v>
@@ -4818,13 +4718,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920239</v>
+        <v>22330051920241</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
         <v>154</v>
@@ -4835,13 +4735,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920240</v>
+        <v>22330051920242</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
         <v>155</v>
@@ -4852,13 +4752,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920241</v>
+        <v>22330051920398</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
         <v>156</v>
@@ -4869,13 +4769,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920242</v>
+        <v>22330051920357</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
         <v>157</v>
@@ -4886,13 +4786,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920398</v>
+        <v>22330051920243</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
         <v>158</v>
@@ -4903,13 +4803,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920357</v>
+        <v>22330051920245</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D19" t="s">
         <v>159</v>
@@ -4920,13 +4820,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920243</v>
+        <v>22330051920369</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D20" t="s">
         <v>160</v>
@@ -4937,13 +4837,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920245</v>
+        <v>22330051920318</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D21" t="s">
         <v>161</v>
@@ -4954,13 +4854,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920369</v>
+        <v>22330051920319</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
         <v>162</v>
@@ -4971,13 +4871,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920318</v>
+        <v>22330051920246</v>
       </c>
       <c r="B23" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
         <v>163</v>
@@ -4988,13 +4888,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920319</v>
+        <v>22330051920249</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
         <v>164</v>
@@ -5005,13 +4905,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920246</v>
+        <v>22330051920414</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
         <v>165</v>
@@ -5022,13 +4922,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920249</v>
+        <v>22330051920248</v>
       </c>
       <c r="B26" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D26" t="s">
         <v>166</v>
@@ -5039,10 +4939,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920414</v>
+        <v>22330051920250</v>
       </c>
       <c r="B27" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
         <v>98</v>
@@ -5056,13 +4956,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920248</v>
+        <v>22330051920251</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>168</v>
@@ -5073,13 +4973,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920250</v>
+        <v>22330051920399</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s">
         <v>169</v>
@@ -5090,13 +4990,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920251</v>
+        <v>22330051920376</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D30" t="s">
         <v>170</v>
@@ -5107,13 +5007,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920399</v>
+        <v>22330051920400</v>
       </c>
       <c r="B31" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D31" t="s">
         <v>171</v>
@@ -5124,13 +5024,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920400</v>
+        <v>22330051920252</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s">
         <v>172</v>
@@ -5141,13 +5041,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920252</v>
+        <v>22330051920253</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
         <v>173</v>
@@ -5158,13 +5058,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920253</v>
+        <v>22330051920235</v>
       </c>
       <c r="B34" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
         <v>174</v>
@@ -5175,13 +5075,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920235</v>
+        <v>22330051920366</v>
       </c>
       <c r="B35" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
         <v>175</v>
@@ -5192,13 +5092,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920366</v>
+        <v>22330051920368</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>142</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
         <v>176</v>
@@ -5209,13 +5109,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920368</v>
+        <v>22330051920254</v>
       </c>
       <c r="B37" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D37" t="s">
         <v>177</v>
@@ -5226,13 +5126,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>22330051920254</v>
+        <v>22330051920255</v>
       </c>
       <c r="B38" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
         <v>178</v>
@@ -5246,10 +5146,10 @@
         <v>22330051920257</v>
       </c>
       <c r="B39" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D39" t="s">
         <v>179</v>
@@ -5263,10 +5163,10 @@
         <v>22330051920256</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D40" t="s">
         <v>180</v>
@@ -5280,10 +5180,10 @@
         <v>22330051920401</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D41" t="s">
         <v>181</v>
@@ -5297,10 +5197,10 @@
         <v>22330051920259</v>
       </c>
       <c r="B42" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C42" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D42" t="s">
         <v>182</v>
@@ -5316,7 +5216,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5348,22 +5248,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920369</v>
+        <v>22330051920233</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5371,22 +5271,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920369</v>
+        <v>22330051920233</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5394,45 +5294,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920231</v>
+        <v>22330051920422</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920232</v>
+        <v>22330051920422</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5440,16 +5340,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920236</v>
+        <v>22330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
         <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5463,22 +5363,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920237</v>
+        <v>22330051920369</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5486,22 +5386,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920239</v>
+        <v>22330051920232</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5509,16 +5409,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920242</v>
+        <v>22330051920236</v>
       </c>
       <c r="B9" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5532,16 +5432,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920400</v>
+        <v>22330051920237</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5555,24 +5455,93 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
+        <v>22330051920239</v>
+      </c>
+      <c r="B11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920242</v>
+      </c>
+      <c r="B12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D12" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920400</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
         <v>22330051920366</v>
       </c>
-      <c r="B11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" t="s">
-        <v>142</v>
-      </c>
-      <c r="D11" t="s">
-        <v>176</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="B14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
         <v>62</v>
       </c>
-      <c r="G11">
+      <c r="G14">
         <v>5</v>
       </c>
     </row>
